--- a/data/trans_camb/IP07_R2-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP07_R2-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-2.84096506350523</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.532151087077315</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.2406852464923011</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.4320502033016038</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-1.590877723815596</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1.038684829797724</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-5.562857845808828</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.71927653688945</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.313921572135178</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-3.213697055441386</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-3.66214174766881</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-1.788478631921117</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>-0.3940709726442664</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>7.323175438018273</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.499350071928582</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6.075024631118926</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.3328552041993301</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>5.924576250828879</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.5830244682765321</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.3144289186578087</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.06124217157786513</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.109934834255388</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.3605686897648596</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.2354154706878109</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.8353113094089456</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.5739937796857916</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.5786964676204699</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.6907010455023077</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6459802036894676</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3717918371725161</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>-0.05161223908096264</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>2.038844890193774</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1.042460203503463</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>2.474622204901793</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1120461816481852</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.572489128333207</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>1.339386712984502</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.490521503598227</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.499018637536587</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.024070349528856</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.07806803858434082</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1.237882533388954</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-0.5314870556168391</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.398697803935284</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.726766848498085</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.62342567404145</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-1.643058909869204</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.464638986390893</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>3.845114821898363</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.0654051808365</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.277307897312507</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.922077583035381</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1.288465449800935</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>3.075716444429593</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>1.145521514114635</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1.274780788154661</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.641265019332766</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.4380869430469013</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.04451979323051111</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.7059262078244622</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.5386172369460198</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.4002766814091508</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.5279587220532935</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.6967598113542233</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2459665574289259</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>10.14246544945038</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>9.571582191386023</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>1.063642626155527</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>3.328158904833076</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.260060960157005</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.773102806295112</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>1.51840021899825</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.002429016427196729</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.04354620607308354</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.846058107100088</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.7617550764293775</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.8611236713099404</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-0.8657321358934106</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.750202887345777</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.006378288798314</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.1339539811595475</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-0.6045306227218243</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.6488164750083792</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>4.46123863828677</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.626528822338396</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.661642652524617</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>4.649522467279149</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.303029445459734</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>2.307767863474668</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>1.225046788564504</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.001959732840048548</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.08686810407315937</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>3.682607102523054</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.8693055516634473</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.9827037735638139</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,20 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.6935885827516513</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.8187168714163089</v>
+      </c>
       <c r="E20" s="6" t="inlineStr"/>
       <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="n">
+        <v>-0.5778399173788004</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.5919526581791434</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1046,18 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>9.873499452502532</v>
+      </c>
       <c r="D21" s="6" t="inlineStr"/>
       <c r="E21" s="6" t="inlineStr"/>
       <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="n">
+        <v>7.866537612878783</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>8.599413883222834</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1070,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-0.8077041537237589</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.345045256734112</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.8387119660470619</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.5175011020445498</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.8245062489364713</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.4185828072048111</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1096,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-3.613508751846736</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-3.269628444348818</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-4.543341553241968</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-3.921989522128216</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-3.020669071979279</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-2.466947728636103</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1122,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>1.012301541223498</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.60081470191586</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.595854216986616</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1.704206235062697</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.6853208170037293</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>1.123040296281583</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1148,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.5893088626664277</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.2517483993080569</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.5075245742078575</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.3131522347357562</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.550403867439341</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.279427349672999</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1022,10 +1179,9 @@
       <c r="E26" s="6" t="inlineStr"/>
       <c r="F26" s="6" t="inlineStr"/>
       <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="n">
+        <v>-0.9096668350826153</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1039,10 +1195,9 @@
       <c r="E27" s="6" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr"/>
       <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="n">
+        <v>2.646606520981564</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1210,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-0.3867028220595228</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-0.1285686585858457</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.5543820944572165</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.2593847592047588</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.4675566922700356</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0.05509780134275721</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1236,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-1.735034388878985</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-1.421515046561369</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-1.800941227209981</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-1.164686940921563</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-1.327840906055278</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-0.974380142210676</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1262,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>0.978226796549362</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>1.322277499426329</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.732828637918595</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>1.861399741821356</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.4595594328754229</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>1.077420966123962</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1288,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.1551040471151239</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.05156807279714606</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.230600607078868</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.1078936053989735</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.1908655387338017</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.02249197094212419</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1314,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.5515066717811608</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.4672319446377575</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.5751337480508925</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.4026851157746223</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.4576613212719375</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.3320099478794563</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1340,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.5430759812376418</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.6998496823215673</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.4534074387012738</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>1.127688416758589</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.2262113801455669</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.521670440096043</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1368,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
